--- a/stories/arbres/TREE-SOC-001.xlsx
+++ b/stories/arbres/TREE-SOC-001.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sara est à la maison, avec maman. Un livre de voyages est ouvert. Maman dit : train. Tchou tchou. Avion. Bzz. Bateau. Floc floc. C'est le nom du véhicule. On voyage avec un adulte. Sara pose le doigt. Maman est l'adulte, tout près. On dit le nom du véhicule. On voyage avec un adulte.</t>
+          <t>Sara est à la maison, avec maman. Un livre de voyages est ouvert. Train. Tchou tchou. Avion. Bzz. Bateau. Floc floc. C'est le nom du véhicule. On voyage avec un adulte. Sara pose le doigt. Maman est l'adulte, tout près. On dit le nom du véhicule. On voyage avec un adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Sara est à la maison, avec maman. Un livre de voyages est ouvert.
+maman|Train. Tchou tchou. Avion. Bzz. Bateau. Floc floc. C'est le nom du véhicule. On voyage avec un adulte.
+narrateur|Sara pose le doigt. Maman est l'adulte, tout près. On dit le nom du véhicule. On voyage avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1511,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1540,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Dans la cuisine, une boîte en forme de train. Le nom du véhicule : train. Maman dit : avec un adulte. Sara répète : train. On dit le nom du véhicule. On voyage avec un adulte.</t>
+          <t>Dans la cuisine, une boîte en forme de train. Le nom du véhicule : train. Avec un adulte. Sara répète : train. On dit le nom du véhicule. On voyage avec un adulte.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1678,13 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Dans la cuisine, une boîte en forme de train. Le nom du véhicule : train.
+maman|Avec un adulte.
+narrateur|Sara répète : train. On dit le nom du véhicule. On voyage avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1861,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Tchou tchou. C'est quel véhicule ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2034,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a dit le nom du véhicule. Train. Avec un adulte. On dit le nom du véhicule. On voyage avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2225,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2392,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Sara prend le ballon rouge. Ça sent le pain tiède. Sara pose le ballon. Maman dit encore : train, avion, bateau. Nom du véhicule. Avec un adulte. On dit le nom du véhicule. On voyage avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2529,6 +2585,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2693,6 +2754,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. La lumière est claire. On pose le ballon. On a dit le nom du véhicule. On reste avec un adulte. Train, tchou tchou. On dit le nom du véhicule. On voyage avec un adulte. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2921,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3088,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. Des miettes dorment sur la table. On secoue le sable. On a dit le nom du véhicule. On reste avec un adulte. Avion, bzz. On dit le nom du véhicule. On voyage avec un adulte. Maman serre Sara tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3255,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3422,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. Un chat miaule une fois. On caresse le tissu. On a dit le nom du véhicule. On reste avec un adulte. Bateau, floc. On dit le nom du véhicule. On voyage avec un adulte. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3589,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3756,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Sara prend le seau bleu. Un ruisseau chante. Le seau devient un port. Bateau. Nom du véhicule. Avec un adulte. On dit le nom du véhicule. On voyage avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3855,6 +3951,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3879,7 +3980,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Tom. Les chaussures font toc toc. On tend la main. On a dit le nom du véhicule. On reste avec un adulte. La main de l'adulte est là. On dit le nom du véhicule. On voyage avec un adulte. Sara range. Maman dit : c'est bien.</t>
+          <t>Sara rejoint Tom. Les chaussures font toc toc. On tend la main. On a dit le nom du véhicule. On reste avec un adulte. La main de l'adulte est là. On dit le nom du véhicule. On voyage avec un adulte. Sara range. C'est bien.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4017,6 +4118,12 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. Les chaussures font toc toc. On tend la main. On a dit le nom du véhicule. On reste avec un adulte. La main de l'adulte est là. On dit le nom du véhicule. On voyage avec un adulte. Sara range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4286,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4453,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. La couverture est douce. On chante un petit air. On a dit le nom du véhicule. On reste avec un adulte. Train, tchou tchou. On dit le nom du véhicule. On voyage avec un adulte. On souffle. Sara sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4620,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4665,6 +4787,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. Une cloche tinte au loin. On compte jusqu'à trois. On a dit le nom du véhicule. On reste avec un adulte. Avion, bzz. On dit le nom du véhicule. On voyage avec un adulte. Sara prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4954,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4851,7 +4983,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Sara prend le doudou. La lumière est claire. Le doudou s'assoit. Sara dit : avion. Avec un adulte. On dit le nom du véhicule. On voyage avec un adulte.</t>
+          <t>Sara prend le doudou. La lumière est claire. Le doudou s'assoit. Avion. Avec un adulte. On dit le nom du véhicule. On voyage avec un adulte.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -4989,6 +5121,12 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Sara prend le doudou. La lumière est claire. Le doudou s'assoit.
+enfant-f|Avion. Avec un adulte. On dit le nom du véhicule. On voyage avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5177,6 +5315,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5341,6 +5484,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. Le bois sent le chaud. On montre du doigt. On a dit le nom du véhicule. On reste avec un adulte. Bateau, floc. On dit le nom du véhicule. On voyage avec un adulte. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5503,6 +5651,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5665,6 +5818,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. Une goutte tombe, ploc. On range la chaise. On a dit le nom du véhicule. On reste avec un adulte. La main de l'adulte est là. On dit le nom du véhicule. On voyage avec un adulte. Maman serre Sara tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5827,6 +5985,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5989,6 +6152,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. Le savon sent la fleur. On range un objet. On a dit le nom du véhicule. On reste avec un adulte. Train, tchou tchou. On dit le nom du véhicule. On voyage avec un adulte. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6151,6 +6319,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6313,6 +6486,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Dans le jardin, un avion de papier. Bzz. Le nom du véhicule : avion. On voyage avec un adulte. Sara tient la main de maman. On dit le nom du véhicule. On voyage avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6489,6 +6667,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Bzz dans le ciel. C'est quoi ?</t>
         </is>
       </c>
     </row>
@@ -6657,6 +6840,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Avion. Le nom du véhicule. Sara reste avec maman. On dit le nom du véhicule. On voyage avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6843,6 +7031,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7005,6 +7198,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Sara prend le ballon rouge. Un nuage passe lentement. Le ballon roule. Train. Tchou. Nom du véhicule. Maman est là. On dit le nom du véhicule. On voyage avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7195,6 +7393,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7219,7 +7422,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Tom. Le tissu est tout doux. On se tient la main. On a dit le nom du véhicule. On reste avec un adulte. Avion, bzz. On dit le nom du véhicule. On voyage avec un adulte. Sara range. Maman dit : c'est bien.</t>
+          <t>Sara rejoint Tom. Le tissu est tout doux. On se tient la main. On a dit le nom du véhicule. On reste avec un adulte. Avion, bzz. On dit le nom du véhicule. On voyage avec un adulte. Sara range. C'est bien.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7357,6 +7560,12 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. Le tissu est tout doux. On se tient la main. On a dit le nom du véhicule. On reste avec un adulte. Avion, bzz. On dit le nom du véhicule. On voyage avec un adulte. Sara range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7519,6 +7728,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7681,6 +7895,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. Une cuillère tinte. On dit merci. On a dit le nom du véhicule. On reste avec un adulte. Bateau, floc. On dit le nom du véhicule. On voyage avec un adulte. On souffle. Sara sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7843,6 +8062,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8005,6 +8229,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. Le sable est tiède. On souffle doucement. On a dit le nom du véhicule. On reste avec un adulte. La main de l'adulte est là. On dit le nom du véhicule. On voyage avec un adulte. Sara prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8167,6 +8396,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8329,6 +8563,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Sara prend le seau bleu. L'eau fait un petit bruit. Sara verse du sable imaginaire. Bateau. Avec un adulte. Nom du véhicule. On dit le nom du véhicule. On voyage avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8517,6 +8756,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8681,6 +8925,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. Un rire court, tout petit. On écoute jusqu'au bout. On a dit le nom du véhicule. On reste avec un adulte. Train, tchou tchou. On dit le nom du véhicule. On voyage avec un adulte. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8843,6 +9092,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9005,6 +9259,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. Le papier froisse, chut. On attend son tour. On a dit le nom du véhicule. On reste avec un adulte. Avion, bzz. On dit le nom du véhicule. On voyage avec un adulte. Maman serre Sara tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9167,6 +9426,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9329,6 +9593,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. L'herbe chatouille le mollet. On sourit ensemble. On a dit le nom du véhicule. On reste avec un adulte. Bateau, floc. On dit le nom du véhicule. On voyage avec un adulte. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9491,6 +9760,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9653,6 +9927,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Sara prend le doudou. Le savon sent la fleur. Le doudou voyage. Sara tient maman. Nom du véhicule. Avec un adulte. On dit le nom du véhicule. On voyage avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9843,6 +10122,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9867,7 +10151,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Tom. Un pigeon roucoule. On pose les pieds par terre. On a dit le nom du véhicule. On reste avec un adulte. La main de l'adulte est là. On dit le nom du véhicule. On voyage avec un adulte. Sara range. Maman dit : c'est bien.</t>
+          <t>Sara rejoint Tom. Un pigeon roucoule. On pose les pieds par terre. On a dit le nom du véhicule. On reste avec un adulte. La main de l'adulte est là. On dit le nom du véhicule. On voyage avec un adulte. Sara range. C'est bien.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10005,6 +10289,12 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. Un pigeon roucoule. On pose les pieds par terre. On a dit le nom du véhicule. On reste avec un adulte. La main de l'adulte est là. On dit le nom du véhicule. On voyage avec un adulte. Sara range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10167,6 +10457,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10329,6 +10624,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. La fenêtre vibre un peu. On parle tout bas. On a dit le nom du véhicule. On reste avec un adulte. Train, tchou tchou. On dit le nom du véhicule. On voyage avec un adulte. On souffle. Sara sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10491,6 +10791,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10653,6 +10958,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. Le lait est froid dans le verre. On range les jouets. On a dit le nom du véhicule. On reste avec un adulte. Avion, bzz. On dit le nom du véhicule. On voyage avec un adulte. Sara prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10815,6 +11125,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10977,6 +11292,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Dans la chambre, un bateau en bois. Floc. Le nom du véhicule : bateau. Avec un adulte. Sara le pose doucement. On dit le nom du véhicule. On voyage avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11153,6 +11473,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Sur l'eau, ça flotte. C'est quoi ?</t>
         </is>
       </c>
     </row>
@@ -11321,6 +11646,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Bateau. Sara a nommé. On voyage avec un adulte. On dit le nom du véhicule. On voyage avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11507,6 +11837,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11669,6 +12004,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Sara prend le ballon rouge. Le coussin est moelleux. Sara lance le ballon, tout doux. Avion. Nom du véhicule. Adulte près. On dit le nom du véhicule. On voyage avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11857,6 +12197,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12021,6 +12366,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. La corde du sac est rêche. On s'assoit un moment. On a dit le nom du véhicule. On reste avec un adulte. Bateau, floc. On dit le nom du véhicule. On voyage avec un adulte. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12183,6 +12533,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12345,6 +12700,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. Le savon mousse entre les doigts. On respire, un, deux. On a dit le nom du véhicule. On reste avec un adulte. La main de l'adulte est là. On dit le nom du véhicule. On voyage avec un adulte. Maman serre Sara tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12507,6 +12867,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12669,6 +13034,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. Un ruisseau chante. On referme le sac. On a dit le nom du véhicule. On reste avec un adulte. Train, tchou tchou. On dit le nom du véhicule. On voyage avec un adulte. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12831,6 +13201,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12993,6 +13368,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Sara prend le seau bleu. Le bois sent le chaud. Le seau tinte. Train. Avec un adulte. Nom du véhicule. On dit le nom du véhicule. On voyage avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13183,6 +13563,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13207,7 +13592,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Tom. La laine gratte un peu. On essuie une miette. On a dit le nom du véhicule. On reste avec un adulte. Avion, bzz. On dit le nom du véhicule. On voyage avec un adulte. Sara range. Maman dit : c'est bien.</t>
+          <t>Sara rejoint Tom. La laine gratte un peu. On essuie une miette. On a dit le nom du véhicule. On reste avec un adulte. Avion, bzz. On dit le nom du véhicule. On voyage avec un adulte. Sara range. C'est bien.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13345,6 +13730,12 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. La laine gratte un peu. On essuie une miette. On a dit le nom du véhicule. On reste avec un adulte. Avion, bzz. On dit le nom du véhicule. On voyage avec un adulte. Sara range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13507,6 +13898,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13669,6 +14065,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. Un pain croustille. On met le doudou près. On a dit le nom du véhicule. On reste avec un adulte. Bateau, floc. On dit le nom du véhicule. On voyage avec un adulte. On souffle. Sara sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13831,6 +14232,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13993,6 +14399,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. Le savon glisse. On lace les chaussures. On a dit le nom du véhicule. On reste avec un adulte. La main de l'adulte est là. On dit le nom du véhicule. On voyage avec un adulte. Sara prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14155,6 +14566,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14317,6 +14733,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Sara prend le doudou. Un vélo passe, toc toc. Sara câline le doudou. Bateau. Nom du véhicule. Avec un adulte. On dit le nom du véhicule. On voyage avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14505,6 +14926,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14669,6 +15095,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. Une plume vole. On met le manteau. On a dit le nom du véhicule. On reste avec un adulte. Train, tchou tchou. On dit le nom du véhicule. On voyage avec un adulte. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14831,6 +15262,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14993,6 +15429,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. Le banc est lisse. On boit une gorgée. On a dit le nom du véhicule. On reste avec un adulte. Avion, bzz. On dit le nom du véhicule. On voyage avec un adulte. Maman serre Sara tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15155,6 +15596,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15317,6 +15763,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. Un grelot sonne. On feuillette le livre. On a dit le nom du véhicule. On reste avec un adulte. Bateau, floc. On dit le nom du véhicule. On voyage avec un adulte. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15479,6 +15930,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15497,7 +15953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15570,6 +16026,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SOC-001.xlsx
+++ b/stories/arbres/TREE-SOC-001.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Sara pose le doigt. Maman est l'adulte, tout près. On dit le nom du véhicule. On voyage avec un adulte.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1516,6 +1522,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1685,6 +1692,7 @@
 narrateur|Sara répète : train. On dit le nom du véhicule. On voyage avec un adulte.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1868,6 +1876,7 @@
           <t>narrateur|Tchou tchou. C'est quel véhicule ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2039,6 +2048,7 @@
           <t>narrateur|Sara a dit le nom du véhicule. Train. Avec un adulte. On dit le nom du véhicule. On voyage avec un adulte.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2230,6 +2240,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2397,6 +2408,7 @@
           <t>narrateur|Sara prend le ballon rouge. Ça sent le pain tiède. Sara pose le ballon. Maman dit encore : train, avion, bateau. Nom du véhicule. Avec un adulte. On dit le nom du véhicule. On voyage avec un adulte.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2592,6 +2604,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2759,6 +2772,7 @@
           <t>narrateur|Sara rejoint Tom. La lumière est claire. On pose le ballon. On a dit le nom du véhicule. On reste avec un adulte. Train, tchou tchou. On dit le nom du véhicule. On voyage avec un adulte. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2926,6 +2940,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3093,6 +3108,7 @@
           <t>narrateur|Sara rejoint Léa. Des miettes dorment sur la table. On secoue le sable. On a dit le nom du véhicule. On reste avec un adulte. Avion, bzz. On dit le nom du véhicule. On voyage avec un adulte. Maman serre Sara tout doux.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3260,6 +3276,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3427,6 +3444,7 @@
           <t>narrateur|Sara rejoint Sami. Un chat miaule une fois. On caresse le tissu. On a dit le nom du véhicule. On reste avec un adulte. Bateau, floc. On dit le nom du véhicule. On voyage avec un adulte. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3594,6 +3612,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3761,6 +3780,7 @@
           <t>narrateur|Sara prend le seau bleu. Un ruisseau chante. Le seau devient un port. Bateau. Nom du véhicule. Avec un adulte. On dit le nom du véhicule. On voyage avec un adulte.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3956,6 +3976,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4124,6 +4145,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4291,6 +4313,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4458,6 +4481,7 @@
           <t>narrateur|Sara rejoint Léa. La couverture est douce. On chante un petit air. On a dit le nom du véhicule. On reste avec un adulte. Train, tchou tchou. On dit le nom du véhicule. On voyage avec un adulte. On souffle. Sara sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4625,6 +4649,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4792,6 +4817,7 @@
           <t>narrateur|Sara rejoint Sami. Une cloche tinte au loin. On compte jusqu'à trois. On a dit le nom du véhicule. On reste avec un adulte. Avion, bzz. On dit le nom du véhicule. On voyage avec un adulte. Sara prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4959,6 +4985,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5127,6 +5154,7 @@
 enfant-f|Avion. Avec un adulte. On dit le nom du véhicule. On voyage avec un adulte.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5322,6 +5350,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5489,6 +5518,7 @@
           <t>narrateur|Sara rejoint Tom. Le bois sent le chaud. On montre du doigt. On a dit le nom du véhicule. On reste avec un adulte. Bateau, floc. On dit le nom du véhicule. On voyage avec un adulte. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5656,6 +5686,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5823,6 +5854,7 @@
           <t>narrateur|Sara rejoint Léa. Une goutte tombe, ploc. On range la chaise. On a dit le nom du véhicule. On reste avec un adulte. La main de l'adulte est là. On dit le nom du véhicule. On voyage avec un adulte. Maman serre Sara tout doux.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5990,6 +6022,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6157,6 +6190,7 @@
           <t>narrateur|Sara rejoint Sami. Le savon sent la fleur. On range un objet. On a dit le nom du véhicule. On reste avec un adulte. Train, tchou tchou. On dit le nom du véhicule. On voyage avec un adulte. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6324,6 +6358,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6491,6 +6526,7 @@
           <t>narrateur|Dans le jardin, un avion de papier. Bzz. Le nom du véhicule : avion. On voyage avec un adulte. Sara tient la main de maman. On dit le nom du véhicule. On voyage avec un adulte.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6674,6 +6710,7 @@
           <t>narrateur|Bzz dans le ciel. C'est quoi ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6845,6 +6882,7 @@
           <t>narrateur|Avion. Le nom du véhicule. Sara reste avec maman. On dit le nom du véhicule. On voyage avec un adulte.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7036,6 +7074,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7203,6 +7242,7 @@
           <t>narrateur|Sara prend le ballon rouge. Un nuage passe lentement. Le ballon roule. Train. Tchou. Nom du véhicule. Maman est là. On dit le nom du véhicule. On voyage avec un adulte.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7398,6 +7438,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7566,6 +7607,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7733,6 +7775,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7900,6 +7943,7 @@
           <t>narrateur|Sara rejoint Léa. Une cuillère tinte. On dit merci. On a dit le nom du véhicule. On reste avec un adulte. Bateau, floc. On dit le nom du véhicule. On voyage avec un adulte. On souffle. Sara sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8067,6 +8111,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8234,6 +8279,7 @@
           <t>narrateur|Sara rejoint Sami. Le sable est tiède. On souffle doucement. On a dit le nom du véhicule. On reste avec un adulte. La main de l'adulte est là. On dit le nom du véhicule. On voyage avec un adulte. Sara prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8401,6 +8447,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8568,6 +8615,7 @@
           <t>narrateur|Sara prend le seau bleu. L'eau fait un petit bruit. Sara verse du sable imaginaire. Bateau. Avec un adulte. Nom du véhicule. On dit le nom du véhicule. On voyage avec un adulte.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8763,6 +8811,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8930,6 +8979,7 @@
           <t>narrateur|Sara rejoint Tom. Un rire court, tout petit. On écoute jusqu'au bout. On a dit le nom du véhicule. On reste avec un adulte. Train, tchou tchou. On dit le nom du véhicule. On voyage avec un adulte. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9097,6 +9147,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9264,6 +9315,7 @@
           <t>narrateur|Sara rejoint Léa. Le papier froisse, chut. On attend son tour. On a dit le nom du véhicule. On reste avec un adulte. Avion, bzz. On dit le nom du véhicule. On voyage avec un adulte. Maman serre Sara tout doux.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9431,6 +9483,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9598,6 +9651,7 @@
           <t>narrateur|Sara rejoint Sami. L'herbe chatouille le mollet. On sourit ensemble. On a dit le nom du véhicule. On reste avec un adulte. Bateau, floc. On dit le nom du véhicule. On voyage avec un adulte. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9765,6 +9819,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9932,6 +9987,7 @@
           <t>narrateur|Sara prend le doudou. Le savon sent la fleur. Le doudou voyage. Sara tient maman. Nom du véhicule. Avec un adulte. On dit le nom du véhicule. On voyage avec un adulte.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10127,6 +10183,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10295,6 +10352,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10462,6 +10520,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10629,6 +10688,7 @@
           <t>narrateur|Sara rejoint Léa. La fenêtre vibre un peu. On parle tout bas. On a dit le nom du véhicule. On reste avec un adulte. Train, tchou tchou. On dit le nom du véhicule. On voyage avec un adulte. On souffle. Sara sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10796,6 +10856,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10963,6 +11024,7 @@
           <t>narrateur|Sara rejoint Sami. Le lait est froid dans le verre. On range les jouets. On a dit le nom du véhicule. On reste avec un adulte. Avion, bzz. On dit le nom du véhicule. On voyage avec un adulte. Sara prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11130,6 +11192,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11297,6 +11360,7 @@
           <t>narrateur|Dans la chambre, un bateau en bois. Floc. Le nom du véhicule : bateau. Avec un adulte. Sara le pose doucement. On dit le nom du véhicule. On voyage avec un adulte.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11480,6 +11544,7 @@
           <t>narrateur|Sur l'eau, ça flotte. C'est quoi ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11651,6 +11716,7 @@
           <t>narrateur|Bateau. Sara a nommé. On voyage avec un adulte. On dit le nom du véhicule. On voyage avec un adulte.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11842,6 +11908,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12009,6 +12076,7 @@
           <t>narrateur|Sara prend le ballon rouge. Le coussin est moelleux. Sara lance le ballon, tout doux. Avion. Nom du véhicule. Adulte près. On dit le nom du véhicule. On voyage avec un adulte.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12204,6 +12272,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12371,6 +12440,7 @@
           <t>narrateur|Sara rejoint Tom. La corde du sac est rêche. On s'assoit un moment. On a dit le nom du véhicule. On reste avec un adulte. Bateau, floc. On dit le nom du véhicule. On voyage avec un adulte. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12538,6 +12608,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12705,6 +12776,7 @@
           <t>narrateur|Sara rejoint Léa. Le savon mousse entre les doigts. On respire, un, deux. On a dit le nom du véhicule. On reste avec un adulte. La main de l'adulte est là. On dit le nom du véhicule. On voyage avec un adulte. Maman serre Sara tout doux.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12872,6 +12944,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13039,6 +13112,7 @@
           <t>narrateur|Sara rejoint Sami. Un ruisseau chante. On referme le sac. On a dit le nom du véhicule. On reste avec un adulte. Train, tchou tchou. On dit le nom du véhicule. On voyage avec un adulte. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13206,6 +13280,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13373,6 +13448,7 @@
           <t>narrateur|Sara prend le seau bleu. Le bois sent le chaud. Le seau tinte. Train. Avec un adulte. Nom du véhicule. On dit le nom du véhicule. On voyage avec un adulte.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13568,6 +13644,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13736,6 +13813,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13903,6 +13981,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14070,6 +14149,7 @@
           <t>narrateur|Sara rejoint Léa. Un pain croustille. On met le doudou près. On a dit le nom du véhicule. On reste avec un adulte. Bateau, floc. On dit le nom du véhicule. On voyage avec un adulte. On souffle. Sara sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14237,6 +14317,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14404,6 +14485,7 @@
           <t>narrateur|Sara rejoint Sami. Le savon glisse. On lace les chaussures. On a dit le nom du véhicule. On reste avec un adulte. La main de l'adulte est là. On dit le nom du véhicule. On voyage avec un adulte. Sara prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14571,6 +14653,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14738,6 +14821,7 @@
           <t>narrateur|Sara prend le doudou. Un vélo passe, toc toc. Sara câline le doudou. Bateau. Nom du véhicule. Avec un adulte. On dit le nom du véhicule. On voyage avec un adulte.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14933,6 +15017,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15100,6 +15185,7 @@
           <t>narrateur|Sara rejoint Tom. Une plume vole. On met le manteau. On a dit le nom du véhicule. On reste avec un adulte. Train, tchou tchou. On dit le nom du véhicule. On voyage avec un adulte. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15267,6 +15353,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15434,6 +15521,7 @@
           <t>narrateur|Sara rejoint Léa. Le banc est lisse. On boit une gorgée. On a dit le nom du véhicule. On reste avec un adulte. Avion, bzz. On dit le nom du véhicule. On voyage avec un adulte. Maman serre Sara tout doux.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15601,6 +15689,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15768,6 +15857,7 @@
           <t>narrateur|Sara rejoint Sami. Un grelot sonne. On feuillette le livre. On a dit le nom du véhicule. On reste avec un adulte. Bateau, floc. On dit le nom du véhicule. On voyage avec un adulte. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15935,6 +16025,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15953,7 +16044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16033,6 +16124,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16047,7 +16152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16234,6 +16339,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
